--- a/Analysis/03_Hypothesis_Tests/3_H1_H2_correlations.xlsx
+++ b/Analysis/03_Hypothesis_Tests/3_H1_H2_correlations.xlsx
@@ -436,7 +436,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1350507416081187</v>
+        <v>-0.1306187202538339</v>
       </c>
     </row>
     <row r="3">
@@ -446,7 +446,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2953056204959446</v>
+        <v>0.3115833067422187</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.04423973174966697</v>
+        <v>-0.0472178436839608</v>
       </c>
     </row>
     <row r="5">
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7327858573745893</v>
+        <v>0.715536429358772</v>
       </c>
     </row>
   </sheetData>
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.1357054720354562</v>
+        <v>-0.1355543803983783</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2929489203763415</v>
+        <v>0.2934916788521411</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1299162217391395</v>
+        <v>-0.1387409970171099</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3142153494388403</v>
+        <v>0.282183734101059</v>
       </c>
     </row>
     <row r="3">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1969983128100527</v>
+        <v>-0.1868248092468082</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1248623072116548</v>
+        <v>0.1459578283625598</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1859976382361848</v>
+        <v>-0.1800859771732198</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1477832699259778</v>
+        <v>0.1613273423572069</v>
       </c>
     </row>
     <row r="4">
@@ -555,16 +555,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01095414368814686</v>
+        <v>0.006320666817758305</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9326587605240978</v>
+        <v>0.9611132712160892</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.02125193275072054</v>
+        <v>-0.03106019407430605</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8697698291415842</v>
+        <v>0.8106025348367679</v>
       </c>
     </row>
     <row r="5">
@@ -574,16 +574,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2081790939538163</v>
+        <v>0.2029412505351162</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1044423441471275</v>
+        <v>0.1136606273057075</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06069072856084909</v>
+        <v>0.05497831937940753</v>
       </c>
       <c r="E5" t="n">
-        <v>0.639365367904452</v>
+        <v>0.6712660802523062</v>
       </c>
     </row>
     <row r="6">
@@ -593,16 +593,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.09962913808379793</v>
+        <v>-0.1019795972014522</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4410416710385717</v>
+        <v>0.4302839055647593</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1439395902274182</v>
+        <v>0.1365179354277394</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2643621252498872</v>
+        <v>0.2900416183467284</v>
       </c>
     </row>
     <row r="7">
@@ -612,16 +612,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.3355997078895017</v>
+        <v>-0.3298582256805419</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007663357207802475</v>
+        <v>0.008840262916793493</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.09840976052935942</v>
+        <v>-0.09501134085119023</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4466812507193447</v>
+        <v>0.4626080045439052</v>
       </c>
     </row>
     <row r="8">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1784644053284984</v>
+        <v>-0.1800760494573292</v>
       </c>
       <c r="C8" t="n">
-        <v>0.165197367999754</v>
+        <v>0.1613508308837212</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1288638765552932</v>
+        <v>-0.1380441170347824</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3181847442613436</v>
+        <v>0.2846317117344361</v>
       </c>
     </row>
   </sheetData>
@@ -716,7 +716,7 @@
         <v>0.1291581677620811</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2545642265367278</v>
+        <v>0.2454987283120546</v>
       </c>
       <c r="H2" t="n">
         <v>-0.08589559567877918</v>
@@ -744,7 +744,7 @@
         <v>0.1957895797134295</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1860189871823928</v>
+        <v>0.1985092291808315</v>
       </c>
       <c r="H3" t="n">
         <v>0.3384704489939815</v>
@@ -772,7 +772,7 @@
         <v>-0.02903477625846743</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1403389489058447</v>
+        <v>0.1475409836065574</v>
       </c>
       <c r="H4" t="n">
         <v>-0.1895948225932362</v>
@@ -800,7 +800,7 @@
         <v>-0.234217219410239</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2661982825917252</v>
+        <v>-0.2318501170960187</v>
       </c>
       <c r="H5" t="n">
         <v>-0.1809322354007706</v>
@@ -828,7 +828,7 @@
         <v>0.5611531590244965</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.06919953832405852</v>
+        <v>0.03209766752065534</v>
       </c>
       <c r="H6" t="n">
         <v>0.07622564192306812</v>
@@ -856,7 +856,7 @@
         <v>0.8551031200423057</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2119563848807635</v>
+        <v>0.2104454685099846</v>
       </c>
       <c r="H7" t="n">
         <v>0.2357784996600439</v>
@@ -884,7 +884,7 @@
         <v>0.1868751731258342</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4206139356853265</v>
+        <v>0.3848555815768931</v>
       </c>
       <c r="H8" t="n">
         <v>-0.1149555538767596</v>
@@ -963,7 +963,7 @@
         <v>0.3170714809949304</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04586053352725499</v>
+        <v>0.05444681105223159</v>
       </c>
       <c r="H2" t="n">
         <v>0.5068139642270586</v>
@@ -991,7 +991,7 @@
         <v>0.127239932451877</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1477359432465684</v>
+        <v>0.1219379425217779</v>
       </c>
       <c r="H3" t="n">
         <v>0.007128019674438111</v>
@@ -1019,7 +1019,7 @@
         <v>0.8227459435005763</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2766231825943595</v>
+        <v>0.2524692477340965</v>
       </c>
       <c r="H4" t="n">
         <v>0.1399672617101854</v>
@@ -1047,7 +1047,7 @@
         <v>0.06691059112381556</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03650236643023629</v>
+        <v>0.0697961027778185</v>
       </c>
       <c r="H5" t="n">
         <v>0.1593343733981542</v>
@@ -1075,7 +1075,7 @@
         <v>2.092204816339375e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5930438977671485</v>
+        <v>0.8043993285044615</v>
       </c>
       <c r="H6" t="n">
         <v>0.5559656955823499</v>
@@ -1103,7 +1103,7 @@
         <v>9.105627991349257e-19</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09816179024878738</v>
+        <v>0.1006377619936372</v>
       </c>
       <c r="H7" t="n">
         <v>0.06506034274453901</v>
@@ -1131,7 +1131,7 @@
         <v>0.1458472286644692</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0006643354188757204</v>
+        <v>0.002011078281329647</v>
       </c>
       <c r="H8" t="n">
         <v>0.3736299883699499</v>
@@ -1262,72 +1262,72 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sec15</t>
+          <t>sec24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7114828703891751</v>
+        <v>0.787840880884735</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.02334507508805591</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1300812255858924</v>
+        <v>0.2184486631476414</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04911875769032343</v>
+        <v>0.1640966306274615</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2099198866971541</v>
+        <v>-0.2786529764483485</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00822743750919883</v>
+        <v>0.2399691716102233</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1226757283933876</v>
+        <v>0.2041169216982499</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09031390717878204</v>
+        <v>0.07509556838980538</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1138681340195404</v>
+        <v>0.1143136178748989</v>
       </c>
       <c r="K2" t="n">
-        <v>0.935483870967742</v>
+        <v>0.9193548387096775</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sec24</t>
+          <t>sec15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.787840880884735</v>
+        <v>0.7114828703891751</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03002413352658418</v>
+        <v>0.009956328699082067</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2184486631476414</v>
+        <v>0.1300812255858924</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1640966306274615</v>
+        <v>0.04911875769032343</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2786529764483485</v>
+        <v>0.2099198866971541</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2399691716102233</v>
+        <v>0.00822743750919883</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2041169216982499</v>
+        <v>0.1226757283933876</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03605092240308415</v>
+        <v>0.07372561146511762</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1143136178748989</v>
+        <v>0.1138681340195404</v>
       </c>
       <c r="K3" t="n">
         <v>0.9193548387096775</v>
@@ -1343,7 +1343,7 @@
         <v>0.5405991449552966</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02431435161912338</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0.5569575392473969</v>
@@ -1361,13 +1361,13 @@
         <v>0.4071121483645818</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01435778518507961</v>
+        <v>0.05495733989913592</v>
       </c>
       <c r="J4" t="n">
         <v>0.3083214359732978</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8064516129032259</v>
+        <v>0.8225806451612904</v>
       </c>
     </row>
     <row r="5">
@@ -1380,7 +1380,7 @@
         <v>0.489148222275413</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09921013655052739</v>
+        <v>0.1015550045296841</v>
       </c>
       <c r="D5" t="n">
         <v>0.1321127295426907</v>
@@ -1398,7 +1398,7 @@
         <v>0.1295774892219866</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02173459458925909</v>
+        <v>0.02909724697338812</v>
       </c>
       <c r="J5" t="n">
         <v>0.09278043179456574</v>
@@ -1417,7 +1417,7 @@
         <v>0.5720659109364322</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1894662942222624</v>
+        <v>0.1872395685478882</v>
       </c>
       <c r="D6" t="n">
         <v>0.1286420958960197</v>
@@ -1435,7 +1435,7 @@
         <v>0.1148216439046681</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002940494869556345</v>
+        <v>0.01698793415749351</v>
       </c>
       <c r="J6" t="n">
         <v>0.07505448162726225</v>
@@ -1454,7 +1454,7 @@
         <v>0.6876809642844807</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2108879095649088</v>
+        <v>0.2178040069082643</v>
       </c>
       <c r="D7" t="n">
         <v>0.1649437645274995</v>
@@ -1472,7 +1472,7 @@
         <v>0.1348350346406568</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003888987920131606</v>
+        <v>-0.00883706043597874</v>
       </c>
       <c r="J7" t="n">
         <v>0.06032257294599219</v>
@@ -1491,7 +1491,7 @@
         <v>0.571895336520327</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2175647468418478</v>
+        <v>0.2191461141217687</v>
       </c>
       <c r="D8" t="n">
         <v>0.07051133644093927</v>
@@ -1509,13 +1509,13 @@
         <v>0.04029438732864574</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003086607345899264</v>
+        <v>-0.006626595393466397</v>
       </c>
       <c r="J8" t="n">
         <v>-0.04741261361834859</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5161290322580645</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
@@ -1528,7 +1528,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2704901543845801</v>
+        <v>0.268462179680248</v>
       </c>
       <c r="D9" t="n">
         <v>0.02257011189108322</v>
@@ -1546,7 +1546,7 @@
         <v>0.01990000211364723</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.003867078732887797</v>
+        <v>-0.003046202364150849</v>
       </c>
       <c r="J9" t="n">
         <v>0.01264407214773655</v>
@@ -1636,7 +1636,7 @@
         <v>0.03847697442290725</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4267791127204308</v>
+        <v>0.4184397474306021</v>
       </c>
       <c r="D2" t="n">
         <v>0.01792616514987679</v>
@@ -1654,7 +1654,7 @@
         <v>-0.00613649798261512</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.003020500195547004</v>
+        <v>-0.007660333318897475</v>
       </c>
       <c r="J2" t="n">
         <v>0.003550712936359446</v>
@@ -1673,7 +1673,7 @@
         <v>0.1642480739396937</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5503618575209929</v>
+        <v>0.5340638320583172</v>
       </c>
       <c r="D3" t="n">
         <v>0.009510544688683523</v>
@@ -1691,7 +1691,7 @@
         <v>0.002690662810970722</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0005903930743400127</v>
+        <v>-0.0001102402771849444</v>
       </c>
       <c r="J3" t="n">
         <v>0.003542291209441828</v>
@@ -1703,75 +1703,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sec57</t>
+          <t>sec1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09327935949424218</v>
+        <v>0.2437325716404674</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4294680258827999</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01870649349105824</v>
+        <v>0.6167452952044618</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01236841593042687</v>
+        <v>0.6380199568466669</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01068570536964703</v>
+        <v>-0.2998714584562907</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.008979685165807131</v>
+        <v>0.1891156375004895</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006919731104164557</v>
+        <v>0.1879200548187051</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.005041072978767908</v>
+        <v>-0.3951176902621632</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.008277896190790557</v>
+        <v>-0.2892668444583677</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7258064516129031</v>
+        <v>-0.7258064516129032</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sec1</t>
+          <t>sec57</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2437325716404674</v>
+        <v>0.09327935949424218</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9904446051399636</v>
+        <v>0.4188678913364022</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6167452952044618</v>
+        <v>0.01870649349105824</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6380199568466669</v>
+        <v>0.01236841593042687</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2998714584562907</v>
+        <v>-0.01068570536964703</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1891156375004895</v>
+        <v>-0.008979685165807131</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1879200548187051</v>
+        <v>0.006919731104164557</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3465983102620257</v>
+        <v>-0.003415629880049712</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2892668444583677</v>
+        <v>-0.008277896190790557</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7096774193548387</v>
+        <v>-0.7258064516129031</v>
       </c>
     </row>
     <row r="6">
@@ -1784,7 +1784,7 @@
         <v>0.04641586339648113</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3774242545712791</v>
+        <v>0.3688368283897112</v>
       </c>
       <c r="D6" t="n">
         <v>0.1220708105436853</v>
@@ -1802,7 +1802,7 @@
         <v>0.02545999485476377</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0385566981465825</v>
+        <v>-0.02841794116886209</v>
       </c>
       <c r="J6" t="n">
         <v>-0.1007738845132877</v>
@@ -1821,7 +1821,7 @@
         <v>0.2012943077208449</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4570770776682223</v>
+        <v>0.4449838259858848</v>
       </c>
       <c r="D7" t="n">
         <v>0.0140266688154771</v>
@@ -1839,47 +1839,47 @@
         <v>0.007967442147638379</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0001006544914652207</v>
+        <v>0.0011342192007438</v>
       </c>
       <c r="J7" t="n">
         <v>-0.008531098050411856</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6612903225806451</v>
+        <v>-0.6451612903225806</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sec62</t>
+          <t>sec6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1260795490030864</v>
+        <v>0.2194971222998793</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3882176841884978</v>
+        <v>0.4581891321377697</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03682948764360038</v>
+        <v>0.2797001563255134</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03662464975205414</v>
+        <v>0.2948148212665231</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.02306821221721244</v>
+        <v>0.5583409774962689</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.004744877484451731</v>
+        <v>-0.1079316834221973</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01243765136264164</v>
+        <v>0.04603756111107495</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.008881263020780319</v>
+        <v>-0.01561413116556806</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.03198189519815742</v>
+        <v>-0.1563561354841596</v>
       </c>
       <c r="K8" t="n">
         <v>-0.6451612903225806</v>
@@ -1888,38 +1888,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sec6</t>
+          <t>sec62</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2194971222998793</v>
+        <v>0.1260795490030864</v>
       </c>
       <c r="C9" t="n">
-        <v>0.452172605952452</v>
+        <v>0.3794793146420848</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2797001563255134</v>
+        <v>0.03682948764360038</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2948148212665231</v>
+        <v>0.03662464975205414</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5583409774962689</v>
+        <v>-0.02306821221721244</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1079316834221973</v>
+        <v>-0.004744877484451731</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04603756111107495</v>
+        <v>0.01243765136264164</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05911784799055923</v>
+        <v>-0.006021671049115598</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1563561354841596</v>
+        <v>-0.03198189519815742</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6290322580645161</v>
+        <v>-0.6451612903225806</v>
       </c>
     </row>
   </sheetData>
